--- a/Config/Datas/Tables/d_掉落_DropProfileConfig.xlsx
+++ b/Config/Datas/Tables/d_掉落_DropProfileConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbDropProfile" sheetId="1" r:id="R32cda9e9e9c04c61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbDropProfile" sheetId="1" r:id="Raf4072e7b07d4f7a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -359,13 +359,13 @@
         <x:v>experienceValue</x:v>
       </x:c>
       <x:c r="E1" s="7" t="str">
-        <x:v>magnetRadiusMilli</x:v>
+        <x:v>magnetRadiusPixels</x:v>
       </x:c>
       <x:c r="F1" s="7" t="str">
-        <x:v>pickupRadiusMilli</x:v>
+        <x:v>pickupRadiusPixels</x:v>
       </x:c>
       <x:c r="G1" s="7" t="str">
-        <x:v>magnetSpeedMilli</x:v>
+        <x:v>magnetSpeedPixelsPerSecond</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
@@ -382,13 +382,13 @@
         <x:v>int</x:v>
       </x:c>
       <x:c r="E2" s="9" t="str">
-        <x:v>int</x:v>
+        <x:v>float</x:v>
       </x:c>
       <x:c r="F2" s="9" t="str">
-        <x:v>int</x:v>
+        <x:v>float</x:v>
       </x:c>
       <x:c r="G2" s="9" t="str">
-        <x:v>int</x:v>
+        <x:v>float</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
@@ -416,13 +416,13 @@
         <x:v>普通怪单只经验</x:v>
       </x:c>
       <x:c r="E4" s="13" t="str">
-        <x:v>吸附半径，世界单位乘1000</x:v>
+        <x:v>吸附半径，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="F4" s="13" t="str">
-        <x:v>拾取半径，世界单位乘1000</x:v>
+        <x:v>拾取半径，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="G4" s="13" t="str">
-        <x:v>吸附速度，世界单位每秒乘1000</x:v>
+        <x:v>吸附速度，逻辑像素/秒；直接填写像素值，最多3位小数。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -437,13 +437,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:v>3000</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="F5" s="5" t="n">
-        <x:v>350</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:v>6000</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
